--- a/AAII_Financials/Quarterly/JCSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JCSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>JCSE</t>
   </si>
@@ -1131,7 +1131,7 @@
         <v>-1600</v>
       </c>
       <c r="E14" s="3">
-        <v>-1600</v>
+        <v>-1500</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1208,10 +1208,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -3069,11 +3069,11 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>600</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -3410,10 +3410,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F52" s="3">
         <v>2900</v>
@@ -3666,10 +3666,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="E57" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="F57" s="3">
         <v>400</v>
@@ -3802,10 +3802,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="E59" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="F59" s="3">
         <v>5200</v>
@@ -5639,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I89" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J89" s="3">
         <v>-300</v>
@@ -6303,10 +6303,10 @@
         <v>-200</v>
       </c>
       <c r="H100" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I100" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="J100" s="3">
         <v>300</v>
